--- a/assets/translations/English.UK.en-UK.xlsx
+++ b/assets/translations/English.UK.en-UK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mspitschan/Projects/LadenburgConsensusStatements/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A055BFF9-2191-584C-B659-2D69D6CA7CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF7FED1-A7BB-8A40-87BD-1FAD11265D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="680" windowWidth="33380" windowHeight="21660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="920" yWindow="880" windowWidth="17540" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="166">
   <si>
     <t>Number</t>
   </si>
@@ -520,6 +520,81 @@
   </si>
   <si>
     <t>0000-0002-8572-9268</t>
+  </si>
+  <si>
+    <t>Kervezee</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>Stefani</t>
+  </si>
+  <si>
+    <t>Oliver</t>
+  </si>
+  <si>
+    <t>Gordijn</t>
+  </si>
+  <si>
+    <t>Marijke</t>
+  </si>
+  <si>
+    <t>Lok</t>
+  </si>
+  <si>
+    <t>Renske</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leiden University Medical Center, Netherlands </t>
+  </si>
+  <si>
+    <t>Lucerne University of Applied Sciences and Arts, Switzerland</t>
+  </si>
+  <si>
+    <t>Chrono@Work &amp; University of Groningen, Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Research Council of Canada, Canada </t>
+  </si>
+  <si>
+    <t>Stanford University, USA</t>
+  </si>
+  <si>
+    <t>0000-0002-6062-9164</t>
+  </si>
+  <si>
+    <t>0000-0003-0199-6500</t>
+  </si>
+  <si>
+    <t>0000-0001-9521-8085</t>
+  </si>
+  <si>
+    <t>0000-0003-3183-4537</t>
+  </si>
+  <si>
+    <t>0000-0003-1684-5625</t>
+  </si>
+  <si>
+    <t>Veitch</t>
+  </si>
+  <si>
+    <t>Jennifer</t>
+  </si>
+  <si>
+    <t>L.Kervezee@lumc.nl</t>
+  </si>
+  <si>
+    <t>oliver.stefani@hslu.ch</t>
+  </si>
+  <si>
+    <t>marijke.gordijn@chronoatwork.com</t>
+  </si>
+  <si>
+    <t>Jennifer.Veitch@nrc-cnrc.gc.ca</t>
+  </si>
+  <si>
+    <t>rlok@stanford.edu</t>
   </si>
 </sst>
 </file>
@@ -782,7 +857,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -840,10 +915,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1195,10 +1274,10 @@
     </row>
     <row r="2" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>136</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>137</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>101</v>
@@ -1214,20 +1293,104 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="17"/>
+      <c r="A3" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="4" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="8" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
@@ -1244,9 +1407,14 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{800FDBEF-8C24-E947-8AD1-7007D3D5CD1C}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{CCBFB7A8-9E45-7F4D-BE36-B55B3DABBB25}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{515BF128-2C7B-644C-BAF2-FD39514861A7}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{A5EDE9A1-4324-034E-AFFB-270B11E7EF79}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{B3FDF847-B13F-9047-BE6D-76D893A34D61}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{ABF05BDF-7442-0F49-BDDB-35D1D1BF692B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId7"/>
 </worksheet>
 </file>
 
